--- a/s-s-event-bogor/sessions/day-2/clinic/extent/extent_account_template.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/extent/extent_account_template.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extent Account" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extent Time Series" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +52,18 @@
       <name val="Arial"/>
       <color rgb="0030302F"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00717171"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000A5455"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +132,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -812,6 +835,377 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="003B9C7B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystem Extent Time Series</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Track extent across multiple accounting periods. Each closing becomes the next opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ecosystem type</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Year 1
+(ha)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Year 2
+(ha)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Year 3
+(ha)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Year 4
+(ha)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Year 5
+(ha)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Total
+change (ha)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Change
+(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Coral reefs (M1.3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="8">
+        <f>F5-B5</f>
+        <v/>
+      </c>
+      <c r="H5" s="9">
+        <f>IF(B5=0,"",G5/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass (M1.1)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="8">
+        <f>F6-B6</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>IF(B6=0,"",G6/B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Mangroves (MFT1.2)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="8">
+        <f>F7-B7</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(B7=0,"",G7/B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Ecosystem 4 (edit)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="8">
+        <f>F8-B8</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>IF(B8=0,"",G8/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="8">
+        <f>F9-B9</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF(B9=0,"",G9/B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Total accounting area</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="8">
+        <f>F10-B10</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>IF(B10=0,"",G10/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Net change per period</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Ecosystem type</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Period 1-2
+(ha)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Period 2-3
+(ha)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Period 3-4
+(ha)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Period 4-5
+(ha)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Coral reefs (M1.3)</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <f>IF(OR(C5="",B5=""),"",C5-B5)</f>
+        <v/>
+      </c>
+      <c r="C14" s="8">
+        <f>IF(OR(D5="",C5=""),"",D5-C5)</f>
+        <v/>
+      </c>
+      <c r="D14" s="8">
+        <f>IF(OR(E5="",D5=""),"",E5-D5)</f>
+        <v/>
+      </c>
+      <c r="E14" s="8">
+        <f>IF(OR(F5="",E5=""),"",F5-E5)</f>
+        <v/>
+      </c>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass (M1.1)</t>
+        </is>
+      </c>
+      <c r="B15" s="8">
+        <f>IF(OR(C6="",B6=""),"",C6-B6)</f>
+        <v/>
+      </c>
+      <c r="C15" s="8">
+        <f>IF(OR(D6="",C6=""),"",D6-C6)</f>
+        <v/>
+      </c>
+      <c r="D15" s="8">
+        <f>IF(OR(E6="",D6=""),"",E6-D6)</f>
+        <v/>
+      </c>
+      <c r="E15" s="8">
+        <f>IF(OR(F6="",E6=""),"",F6-E6)</f>
+        <v/>
+      </c>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Mangroves (MFT1.2)</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>IF(OR(C7="",B7=""),"",C7-B7)</f>
+        <v/>
+      </c>
+      <c r="C16" s="8">
+        <f>IF(OR(D7="",C7=""),"",D7-C7)</f>
+        <v/>
+      </c>
+      <c r="D16" s="8">
+        <f>IF(OR(E7="",D7=""),"",E7-D7)</f>
+        <v/>
+      </c>
+      <c r="E16" s="8">
+        <f>IF(OR(F7="",E7=""),"",F7-E7)</f>
+        <v/>
+      </c>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Ecosystem 4 (edit)</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>IF(OR(C8="",B8=""),"",C8-B8)</f>
+        <v/>
+      </c>
+      <c r="C17" s="8">
+        <f>IF(OR(D8="",C8=""),"",D8-C8)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>IF(OR(E8="",D8=""),"",E8-D8)</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>IF(OR(F8="",E8=""),"",F8-E8)</f>
+        <v/>
+      </c>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>IF(OR(C9="",B9=""),"",C9-B9)</f>
+        <v/>
+      </c>
+      <c r="C18" s="8">
+        <f>IF(OR(D9="",C9=""),"",D9-C9)</f>
+        <v/>
+      </c>
+      <c r="D18" s="8">
+        <f>IF(OR(E9="",D9=""),"",E9-D9)</f>
+        <v/>
+      </c>
+      <c r="E18" s="8">
+        <f>IF(OR(F9="",E9=""),"",F9-E9)</f>
+        <v/>
+      </c>
+      <c r="F18" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000A5455"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -836,7 +1230,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Opening \ Closing</t>
         </is>
@@ -883,7 +1277,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="8">
+      <c r="G4" s="12">
         <f>SUM(B4:F4)</f>
         <v/>
       </c>
@@ -899,7 +1293,7 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="8">
+      <c r="G5" s="12">
         <f>SUM(B5:F5)</f>
         <v/>
       </c>
@@ -915,7 +1309,7 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8">
+      <c r="G6" s="12">
         <f>SUM(B6:F6)</f>
         <v/>
       </c>
@@ -931,7 +1325,7 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="8">
+      <c r="G7" s="12">
         <f>SUM(B7:F7)</f>
         <v/>
       </c>
@@ -947,34 +1341,34 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="8">
+      <c r="G8" s="12">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Closing total</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="12">
         <f>SUM(B4:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="12">
         <f>SUM(C4:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="12">
         <f>SUM(E4:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="12">
         <f>SUM(F4:F8)</f>
         <v/>
       </c>
@@ -984,7 +1378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1004,56 +1398,56 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>1. Fill in the yellow cells with your data.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2. On the Extent Account sheet, enter area values in hectares.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>3. Total additions, reductions, net change, and closing extent calculate automatically.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>4. On the Change Matrix sheet, enter the cross-tabulation of opening vs closing classifications.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>5. Row totals (opening extent per type) and column totals (closing extent per type) calculate automatically.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>6. The Total column on the Extent Account sums across all ecosystem types.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>7. Adapt the ecosystem type names and IUCN GET codes to your accounting area.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>8. Delete Ecosystem 4 column if not needed, or add more columns as required.</t>
         </is>

--- a/s-s-event-bogor/sessions/day-2/clinic/extent/extent_account_template.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/extent/extent_account_template.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extent Account" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extent Time Series" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extent Account" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extent Time Series" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +66,11 @@
       <b val="1"/>
       <color rgb="000A5455"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="003B9C7B"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -118,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +152,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,6 +520,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000A5455"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ocean Accounting Clinic: Extent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Account Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>How to use this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Fill in the yellow cells with your country's data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>White cells with formulas will calculate automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>See the Glossary sheet for definitions of all terms and abbreviations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>See the Instructions sheet (if present) for detailed step-by-step guidance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="003B9C7B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -554,6 +634,7 @@
       </c>
       <c r="B4" s="3" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
@@ -832,7 +913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003B9C7B"/>
@@ -866,6 +947,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1035,6 +1117,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -1203,7 +1286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000A5455"/>
@@ -1229,6 +1312,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1378,7 +1462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1397,6 +1481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1452,6 +1537,504 @@
           <t>8. Delete Ecosystem 4 column if not needed, or add more columns as required.</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003B9C7B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Glossary of Terms and Abbreviations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Term / Abbreviation</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Gross Value Added</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Total output minus intermediate consumption. The value an industry adds to the economy.</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Currency (e.g., USD, local currency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Total value of goods and services produced in a country. Sum of GVA across all industries plus taxes minus subsidies.</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Intermediate Consumption</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>The value of goods and services consumed as inputs during production (e.g., fuel, raw materials, purchased services). Does not include fixed assets.</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Gross Output</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Total value of goods and services produced by an industry before deducting input costs. Also called gross sales or turnover.</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>SUT</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Supply-Use Tables</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Statistical tables from the national accounts showing what each industry produces (supply) and what each industry consumes (use). Published by the National Statistical Office.</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>System of National Accounts</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>The international statistical standard for measuring economic activity. Published by the UN. The basis for GDP calculation.</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>SEEA-EA</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>System of Environmental-Economic Accounting - Ecosystem Accounting</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>The international statistical standard for measuring ecosystems, their condition, and the services they provide.</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>OESA</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Ocean Economy Satellite Account</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>A satellite account that reorganizes national accounts to identify the market-based ocean economy. Reports GDP-compatible indicators.</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>OTSA</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Ocean Tourism Satellite Account</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>A satellite account focused on coastal and marine tourism's economic contribution. A subset of OESA.</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Ocean Economy Partial</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>The share (0 to 1) of a mixed industry's output that is ocean-related. For example, if 30% of construction is coastal, the partial is 0.30.</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Proportion (0 to 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Condition Index</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>A normalized score from 0 (fully degraded) to 1 (reference/healthy condition). Used in SEEA-EA condition accounts.</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Index (0 to 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>NCP</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Net Carbon Production</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>The rate at which an ecosystem sequesters carbon dioxide per unit area per year.</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Mg CO2/ha/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>SCC</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Social Cost of Carbon</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>An estimate of the economic damage caused by emitting one additional tonne of CO2. Used to value carbon sequestration.</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>USD per Mg CO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Mg CO2</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Megagrams of CO2</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Metric tonnes of carbon dioxide. 1 Mg = 1 tonne = 1,000 kg.</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>ha</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Hectares</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Unit of area. 1 hectare = 10,000 square metres = 0.01 square kilometres.</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Kilograms per year</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Physical quantity measured in kilograms over one year.</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Mass per time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>USD million</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>United States Dollars, millions</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Monetary values expressed in millions of US dollars. For example, USD 132.5 million = USD 132,500,000.</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>R million</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>South African Rand, millions</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Monetary values in the South Africa example are in millions of Rand.</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>ISIC</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>International Standard Industrial Classification</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>The UN classification system for economic activities. Used to map industries to ocean economy groups.</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>SIC</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Standard Industrial Classification</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>National classification system for economic activities. Varies by country but based on ISIC.</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Exclusive Economic Zone</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Maritime zone extending 200 nautical miles from a country's coastline, within which the country has rights to marine resources.</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Red-Amber-Green</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>A confidence rating system. Green = high confidence (direct evidence). Amber = moderate (proxy data). Red = low (sparse evidence).</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
